--- a/event_feedback_forms/013_real_time_feedback_tracker--event_feedback_forms.xlsx
+++ b/event_feedback_forms/013_real_time_feedback_tracker--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'pacific_time_(us_&amp;_canada)'}</t>
+          <t>pacific_time_(us_&amp;_canada)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Pacific Time (US &amp; Canada)'}</t>
+          <t>Pacific Time (US &amp; Canada)</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'central_time_(us_&amp;_canada)'}</t>
+          <t>central_time_(us_&amp;_canada)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Central Time (US &amp; Canada)'}</t>
+          <t>Central Time (US &amp; Canada)</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'eastern_time_(us_&amp;_canada)'}</t>
+          <t>eastern_time_(us_&amp;_canada)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Eastern Time (US &amp; Canada)'}</t>
+          <t>Eastern Time (US &amp; Canada)</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'atlantic_time_(canada)'}</t>
+          <t>atlantic_time_(canada)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Atlantic Time (Canada)'}</t>
+          <t>Atlantic Time (Canada)</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'australia_time_(eastern)'}</t>
+          <t>australia_time_(eastern)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Australia Time (Eastern)'}</t>
+          <t>Australia Time (Eastern)</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'australia_time_(central)'}</t>
+          <t>australia_time_(central)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Australia Time (Central)'}</t>
+          <t>Australia Time (Central)</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'australia_time_(western)'}</t>
+          <t>australia_time_(western)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Australia Time (Western)'}</t>
+          <t>Australia Time (Western)</t>
         </is>
       </c>
     </row>
